--- a/scripts/productos-digitales/guia-pasteleria/build/plan-financiero-3-anos-pasteleria.xlsx
+++ b/scripts/productos-digitales/guia-pasteleria/build/plan-financiero-3-anos-pasteleria.xlsx
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B12" s="16">
         <f>IFERROR(SUMPRODUCT('Tesorería 12 meses'!B6:M6,'Tesorería 12 meses'!B7:M7),"")</f>
-        <v>0.8816511800000001</v>
+        <v>0.87639985</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="B10" s="16">
         <f>IFERROR('0. Supuestos'!$B$12,"")</f>
-        <v>0.8816511800000001</v>
+        <v>0.87639985</v>
       </c>
       <c r="C10" s="17" t="n">
         <v>1</v>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="B11" s="24">
         <f>IFERROR(IF(B7*B8*B9*B10=0,"",B7*B8*B9*B10),"")</f>
-        <v>284066.134636376</v>
+        <v>282374.1672816677</v>
       </c>
       <c r="C11" s="24">
         <f>IFERROR(IF(C7*C8*C9*C10=0,"",C7*C8*C9*C10),"")</f>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="B12" s="15">
         <f>IFERROR(IF(B11="","",B11*(1-'0. Supuestos'!$B$19)),"")</f>
-        <v>226890.4393213048</v>
+        <v>225539.02438788276</v>
       </c>
       <c r="C12" s="15">
         <f>IFERROR(IF(C11="","",C11*(1-'0. Supuestos'!$B$19)),"")</f>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="B13" s="15">
         <f>IFERROR(IF(B11="","",B11*'0. Supuestos'!$B$19),"")</f>
-        <v>57175.695315071214</v>
+        <v>56835.14289378495</v>
       </c>
       <c r="C13" s="15">
         <f>IFERROR(IF(C11="","",C11*'0. Supuestos'!$B$19),"")</f>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="B15" s="15">
         <f>IFERROR(IF(B11="","",B11*'0. Supuestos'!$B$22),"")</f>
-        <v>90901.16308364032</v>
+        <v>90359.73353013367</v>
       </c>
       <c r="C15" s="15">
         <f>IFERROR(IF(C11="","",C11*'0. Supuestos'!$B$22),"")</f>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B16" s="24">
         <f>IFERROR(IF(B11="","",SUM(B15:B15)),"")</f>
-        <v>90901.16308364032</v>
+        <v>90359.73353013367</v>
       </c>
       <c r="C16" s="24">
         <f>IFERROR(IF(C11="","",SUM(C15:C15)),"")</f>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B17" s="24">
         <f>IFERROR(IF(B11="","",B11-B16),"")</f>
-        <v>193164.97155273566</v>
+        <v>192014.43375153403</v>
       </c>
       <c r="C17" s="24">
         <f>IFERROR(IF(C11="","",C11-C16),"")</f>
@@ -3459,6 +3459,10 @@
         <f>IFERROR(IF(D11="","",'Personal'!$I$11),"")</f>
         <v>92776.0785</v>
       </c>
+      <c r="E19" s="16">
+        <f>IFERROR(C19/$C$11,"")</f>
+        <v>0.287947520354731</v>
+      </c>
       <c r="F19" s="16" t="n">
         <v>0</v>
       </c>
@@ -3898,7 +3902,7 @@
       </c>
       <c r="B34" s="15">
         <f>IFERROR(IF(B11="","",B15*$F$15),"")</f>
-        <v>9090.116308364033</v>
+        <v>9035.973353013367</v>
       </c>
       <c r="C34" s="15">
         <f>IFERROR(IF(C11="","",C15*$F$15),"")</f>
@@ -3941,7 +3945,7 @@
       </c>
       <c r="B36" s="24">
         <f>IFERROR(IF(B11="","",B17-B33),"")</f>
-        <v>6407.754234044405</v>
+        <v>5257.216432842775</v>
       </c>
       <c r="C36" s="24">
         <f>IFERROR(IF(C11="","",C17-C33),"")</f>
@@ -3990,7 +3994,7 @@
       </c>
       <c r="B38" s="15">
         <f>IFERROR(IF(B11="","",MAX(0,B36-B37)),"")</f>
-        <v>6407.754234044405</v>
+        <v>5257.216432842775</v>
       </c>
       <c r="C38" s="15">
         <f>IFERROR(IF(C11="","",MAX(0,C36-C37)),"")</f>
@@ -4052,7 +4056,7 @@
       </c>
       <c r="B41" s="15">
         <f>IFERROR(IF(B11="","",IF(B40="",0,B38*B40)),"")</f>
-        <v>961.1631351066608</v>
+        <v>788.5824649264163</v>
       </c>
       <c r="C41" s="15">
         <f>IFERROR(IF(C11="","",IF(C40="",0,C38*C40)),"")</f>
@@ -4090,7 +4094,7 @@
       </c>
       <c r="B43" s="24">
         <f>IFERROR(IF(B11="","",B36-B41),"")</f>
-        <v>5446.591098937744</v>
+        <v>4468.633967916359</v>
       </c>
       <c r="C43" s="24">
         <f>IFERROR(IF(C11="","",C36-C41),"")</f>
@@ -4217,7 +4221,7 @@
       </c>
       <c r="B48" s="16">
         <f>IFERROR(IF(B11="","",B19/B11),"")</f>
-        <v>0.326600277849944</v>
+        <v>0.32855724513728635</v>
       </c>
       <c r="C48" s="16">
         <f>IFERROR(IF(C11="","",C19/C11),"")</f>
@@ -4245,7 +4249,7 @@
       </c>
       <c r="B49" s="16">
         <f>IFERROR(IF(B11="","",B21/B11),"")</f>
-        <v>0.05069242068729164</v>
+        <v>0.05099616632294847</v>
       </c>
       <c r="C49" s="16">
         <f>IFERROR(IF(C11="","",C21/C11),"")</f>
@@ -4273,7 +4277,7 @@
       </c>
       <c r="B50" s="16">
         <f>IFERROR(IF(B11="","",B43/B11),"")</f>
-        <v>0.019173672729097934</v>
+        <v>0.015825222296127765</v>
       </c>
       <c r="C50" s="16">
         <f>IFERROR(IF(C11="","",C43/C11),"")</f>
@@ -4520,7 +4524,7 @@
       </c>
       <c r="B10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",'PyG 3 Años'!B16/('PyG 3 Años'!B7*'PyG 3 Años'!B9*'PyG 3 Años'!B10)),"")</f>
-        <v>1.8780203871698915</v>
+        <v>1.878020387169892</v>
       </c>
       <c r="C10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",'PyG 3 Años'!C16/('PyG 3 Años'!C7*'PyG 3 Años'!C9*'PyG 3 Años'!C10)),"")</f>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="B11" s="15">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",B9-B10),"")</f>
-        <v>3.9907933227360197</v>
+        <v>3.9907933227360193</v>
       </c>
       <c r="C11" s="15">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",C9-C10),"")</f>
@@ -4622,7 +4626,7 @@
       </c>
       <c r="B15" s="27">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",IF(B11&lt;=0,"",B7/B11)),"")</f>
-        <v>46797.015584523855</v>
+        <v>46797.01558452386</v>
       </c>
       <c r="C15" s="27">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",IF(C11&lt;=0,"",C7/C11)),"")</f>
@@ -4641,7 +4645,7 @@
       </c>
       <c r="B16" s="20">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",B15/B12),"")</f>
-        <v>155.99005194841286</v>
+        <v>155.99005194841288</v>
       </c>
       <c r="C16" s="20">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",C15/C12),"")</f>
@@ -4735,7 +4739,7 @@
       </c>
       <c r="B21" s="27">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",IF(B11&lt;=0,"",B20/B11)),"")</f>
-        <v>43719.50609606207</v>
+        <v>43719.506096062076</v>
       </c>
       <c r="C21" s="27">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",IF(C11&lt;=0,"",C20/C11)),"")</f>
@@ -4754,7 +4758,7 @@
       </c>
       <c r="B22" s="31">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",B21/B12),"")</f>
-        <v>145.73168698687357</v>
+        <v>145.7316869868736</v>
       </c>
       <c r="C22" s="31">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",C21/C12),"")</f>
@@ -4774,7 +4778,7 @@
       </c>
       <c r="B23" s="15">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",B21*B9),"")</f>
-        <v>256581.63676688413</v>
+        <v>256581.63676688418</v>
       </c>
       <c r="C23" s="15">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",C21*C9),"")</f>
@@ -4804,7 +4808,7 @@
       </c>
       <c r="B25" s="20">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",'PyG 3 Años'!B7*'PyG 3 Años'!B10),"")</f>
-        <v>161.34216594000003</v>
+        <v>160.38117255</v>
       </c>
       <c r="C25" s="20">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",'PyG 3 Años'!C7*'PyG 3 Años'!C10),"")</f>
@@ -4823,7 +4827,7 @@
       </c>
       <c r="B26" s="16">
         <f>IFERROR(IF('PyG 3 Años'!B11="","",IF(B22&lt;=0,"",B25/B22-1)),"")</f>
-        <v>0.10711794583516032</v>
+        <v>0.10052368064912276</v>
       </c>
       <c r="C26" s="16">
         <f>IFERROR(IF('PyG 3 Años'!C11="","",IF(C22&lt;=0,"",C25/C22-1)),"")</f>
@@ -5472,7 +5476,7 @@
       </c>
       <c r="C23" s="15">
         <f>IFERROR(IF(C9="","",'Tesorería 12 meses'!M23),"")</f>
-        <v>96748.14803126662</v>
+        <v>95212.51766301482</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -6382,44 +6386,44 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>0.098333</v>
+        <v>0.111667</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>0.078333</v>
+        <v>0.0775</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>0.081667</v>
+        <v>0.080833</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08666699999999999</v>
       </c>
       <c r="F6" s="18" t="n">
+        <v>0.089167</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.080833</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.07083299999999999</v>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>0.054167</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0.075833</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0.079167</v>
+      </c>
+      <c r="L6" s="18" t="n">
         <v>0.09</v>
       </c>
-      <c r="G6" s="18" t="n">
-        <v>0.081667</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>0.07166699999999999</v>
-      </c>
-      <c r="I6" s="18" t="n">
-        <v>0.056667</v>
-      </c>
-      <c r="J6" s="18" t="n">
-        <v>0.076667</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="L6" s="18" t="n">
-        <v>0.090833</v>
-      </c>
       <c r="M6" s="18" t="n">
-        <v>0.106667</v>
+        <v>0.103333</v>
       </c>
       <c r="N6" s="16">
         <f>IFERROR(SUM(B6:M6),"")</f>
-        <v>1.0000010000000001</v>
+        <v>1.0</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -6495,51 +6499,51 @@
       </c>
       <c r="B8" s="19">
         <f>IFERROR(B6*B7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.06134302457350536</v>
+        <v>0.07007857201253516</v>
       </c>
       <c r="C8" s="19">
         <f>IFERROR(C6*C7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.05686276062149659</v>
+        <v>0.05659517171300292</v>
       </c>
       <c r="D8" s="19">
         <f>IFERROR(D6*D7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.06761961119362421</v>
+        <v>0.06733010052432117</v>
       </c>
       <c r="E8" s="19">
         <f>IFERROR(E6*E7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.081381391674653</v>
+        <v>0.08108963049229184</v>
       </c>
       <c r="F8" s="19">
         <f>IFERROR(F6*F7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.09289388122862831</v>
+        <v>0.09258555897744619</v>
       </c>
       <c r="G8" s="19">
         <f>IFERROR(G6*G7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.09262960437482769</v>
+        <v>0.09223301441687833</v>
       </c>
       <c r="H8" s="19">
         <f>IFERROR(H6*H7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.08128725013445792</v>
+        <v>0.08082269753925676</v>
       </c>
       <c r="I8" s="19">
         <f>IFERROR(I6*I7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.0642737187739033</v>
+        <v>0.061806263431012684</v>
       </c>
       <c r="J8" s="19">
         <f>IFERROR(J6*J7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.08695842725464281</v>
+        <v>0.08652785597806754</v>
       </c>
       <c r="K8" s="19">
         <f>IFERROR(K6*K7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.09073883392295805</v>
+        <v>0.09033205562506658</v>
       </c>
       <c r="L8" s="19">
         <f>IFERROR(L6*L7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.1030260062715506</v>
+        <v>0.102692851898594</v>
       </c>
       <c r="M8" s="19">
         <f>IFERROR(M6*M7/SUMPRODUCT($B$6:$M$6,$B$7:$M$7),"")</f>
-        <v>0.12098548997575208</v>
+        <v>0.11790622739152683</v>
       </c>
       <c r="N8" s="16">
         <f>IFERROR(SUM(B8:M8),"")</f>
@@ -6580,55 +6584,55 @@
       </c>
       <c r="B10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(B8*(1-'0. Supuestos'!$B$52/30))),"")</f>
-        <v>17535.7648857652</v>
+        <v>19913.62266480981</v>
       </c>
       <c r="C10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(C8*(1-'0. Supuestos'!$B$52/30)+B8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>17676.837302655556</v>
+        <v>17696.779287743502</v>
       </c>
       <c r="D10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(D8*(1-'0. Supuestos'!$B$52/30)+C8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>20647.98977532122</v>
+        <v>20436.57227462415</v>
       </c>
       <c r="E10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(E8*(1-'0. Supuestos'!$B$52/30)+D8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>24831.312016230786</v>
+        <v>24593.83303674873</v>
       </c>
       <c r="F10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(F8*(1-'0. Supuestos'!$B$52/30)+E8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>28441.29162624751</v>
+        <v>28177.552857546325</v>
       </c>
       <c r="G10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(G8*(1-'0. Supuestos'!$B$52/30)+F8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>28632.582764855553</v>
+        <v>28342.240778481268</v>
       </c>
       <c r="H10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(H8*(1-'0. Supuestos'!$B$52/30)+G8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>25384.086095706</v>
+        <v>25091.746896294004</v>
       </c>
       <c r="I10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(I8*(1-'0. Supuestos'!$B$52/30)+H8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>20257.634307456003</v>
+        <v>19425.116063375106</v>
       </c>
       <c r="J10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(J8*(1-'0. Supuestos'!$B$52/30)+I8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>26348.034295206005</v>
+        <v>26011.89679487491</v>
       </c>
       <c r="K10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(K8*(1-'0. Supuestos'!$B$52/30)+J8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>27954.50654866546</v>
+        <v>27662.491586375105</v>
       </c>
       <c r="L10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(L8*(1-'0. Supuestos'!$B$52/30)+K8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>31554.59017883446</v>
+        <v>31262.60150604046</v>
       </c>
       <c r="M10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*(1+'0. Supuestos'!$B$20)*(M8*(1-'0. Supuestos'!$B$52/30)+L8*('0. Supuestos'!$B$52/30))),"")</f>
-        <v>36973.35487700011</v>
+        <v>35870.44916295946</v>
       </c>
       <c r="N10" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(B10:M10)),"")</f>
-        <v>306237.98467394384</v>
+        <v>304484.9029098729</v>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
@@ -6664,56 +6668,56 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(B8*(1-'0. Supuestos'!$B$53/30))),"")</f>
-        <v>-0.0</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(B8*(1-'0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>0.0</v>
       </c>
       <c r="C12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(C8*(1-'0. Supuestos'!$B$53/30)+B8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-6133.767508879963</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(C8*(1-'0. Supuestos'!$B$53/30)+B8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-6965.509202547458</v>
       </c>
       <c r="D12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(D8*(1-'0. Supuestos'!$B$53/30)+C8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-5685.780184304729</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(D8*(1-'0. Supuestos'!$B$53/30)+C8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-5625.317098587014</v>
       </c>
       <c r="E12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(E8*(1-'0. Supuestos'!$B$53/30)+D8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-6761.371435240384</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(E8*(1-'0. Supuestos'!$B$53/30)+D8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-6692.322936128253</v>
       </c>
       <c r="F12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(F8*(1-'0. Supuestos'!$B$53/30)+E8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-8137.4294722503655</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(F8*(1-'0. Supuestos'!$B$53/30)+E8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-8059.961143674544</v>
       </c>
       <c r="G12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(G8*(1-'0. Supuestos'!$B$53/30)+F8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-9288.578031739442</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(G8*(1-'0. Supuestos'!$B$53/30)+F8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-9202.607081734566</v>
       </c>
       <c r="H12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(H8*(1-'0. Supuestos'!$B$53/30)+G8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-9262.152651014225</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(H8*(1-'0. Supuestos'!$B$53/30)+G8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-9167.565665929114</v>
       </c>
       <c r="I12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(I8*(1-'0. Supuestos'!$B$53/30)+H8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-8128.0161392023265</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(I8*(1-'0. Supuestos'!$B$53/30)+H8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-8033.429154117216</v>
       </c>
       <c r="J12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(J8*(1-'0. Supuestos'!$B$53/30)+I8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-6426.81137148448</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(J8*(1-'0. Supuestos'!$B$53/30)+I8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-6143.277243531507</v>
       </c>
       <c r="K12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(K8*(1-'0. Supuestos'!$B$53/30)+J8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-8695.084395108277</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(K8*(1-'0. Supuestos'!$B$53/30)+J8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-8600.497410023165</v>
       </c>
       <c r="L12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(L8*(1-'0. Supuestos'!$B$53/30)+K8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-9073.092094495181</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(L8*(1-'0. Supuestos'!$B$53/30)+K8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-8978.618523061252</v>
       </c>
       <c r="M12" s="15">
-        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(M8*(1-'0. Supuestos'!$B$53/30)+L8*('0. Supuestos'!$B$53/30))),"")</f>
-        <v>-10301.70217774101</v>
+        <f>IFERROR(IF('PyG 3 Años'!$B$11="","",-'PyG 3 Años'!$B$15*(1+'PyG 3 Años'!$F$15)*(M8*(1-'0. Supuestos'!$B$53/30)+L8*('0. Supuestos'!$B$53/30))+0),"")</f>
+        <v>-10207.22860630708</v>
       </c>
       <c r="N12" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(B12:M12)),"")</f>
-        <v>-87893.78546146039</v>
+        <v>-87676.33406564116</v>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
@@ -6980,55 +6984,55 @@
       </c>
       <c r="B17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*B8*'0. Supuestos'!$B$20),"")</f>
-        <v>1532.1077827868096</v>
+        <v>1739.86230238531</v>
       </c>
       <c r="C17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*C8*'0. Supuestos'!$B$20),"")</f>
-        <v>1420.208388886096</v>
+        <v>1405.1057681778104</v>
       </c>
       <c r="D17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*D8*'0. Supuestos'!$B$20),"")</f>
-        <v>1688.8722605229311</v>
+        <v>1671.6251537934552</v>
       </c>
       <c r="E17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*E8*'0. Supuestos'!$B$20),"")</f>
-        <v>2032.5874771523768</v>
+        <v>2013.2372443698862</v>
       </c>
       <c r="F17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*F8*'0. Supuestos'!$B$20),"")</f>
-        <v>2320.124242212957</v>
+        <v>2298.650203393364</v>
       </c>
       <c r="G17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*G8*'0. Supuestos'!$B$20),"")</f>
-        <v>2313.5236445519604</v>
+        <v>2289.8974709499385</v>
       </c>
       <c r="H17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*H8*'0. Supuestos'!$B$20),"")</f>
-        <v>2030.236191290305</v>
+        <v>2006.6100176882833</v>
       </c>
       <c r="I17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*I8*'0. Supuestos'!$B$20),"")</f>
-        <v>1605.3050113978222</v>
+        <v>1534.4831480824087</v>
       </c>
       <c r="J17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*J8*'0. Supuestos'!$B$20),"")</f>
-        <v>2171.879917921133</v>
+        <v>2148.253744319111</v>
       </c>
       <c r="K17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*K8*'0. Supuestos'!$B$20),"")</f>
-        <v>2266.2996260932428</v>
+        <v>2242.7017812365466</v>
       </c>
       <c r="L17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*L8*'0. Supuestos'!$B$20),"")</f>
-        <v>2573.1849242115936</v>
+        <v>2549.587079354898</v>
       </c>
       <c r="M17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$11*M8*'0. Supuestos'!$B$20),"")</f>
-        <v>3021.742277706099</v>
+        <v>2927.294240788663</v>
       </c>
       <c r="N17" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(B17:M17)),"")</f>
-        <v>24976.071744733326</v>
+        <v>24827.308154539674</v>
       </c>
     </row>
     <row r="18">
@@ -7039,55 +7043,55 @@
       </c>
       <c r="B18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*B8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1327.2652280799966</v>
+        <v>1402.8781093224961</v>
       </c>
       <c r="C18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*C8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1286.5391076640663</v>
+        <v>1281.0424635079103</v>
       </c>
       <c r="D18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*D8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1384.3201304763984</v>
+        <v>1378.0429941934774</v>
       </c>
       <c r="E18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*E8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1509.4163156591242</v>
+        <v>1502.3737403340492</v>
       </c>
       <c r="F18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*F8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1614.0661847035858</v>
+        <v>1606.2506437940513</v>
       </c>
       <c r="G18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*G8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1611.6638773649295</v>
+        <v>1603.0650605390101</v>
       </c>
       <c r="H18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*H8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1508.5605581093023</v>
+        <v>1499.9617412833832</v>
       </c>
       <c r="I18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*I8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1353.9055792258619</v>
+        <v>1328.1297494119551</v>
       </c>
       <c r="J18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*J8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1560.112217737116</v>
+        <v>1551.5134009111966</v>
       </c>
       <c r="K18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*K8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1594.4765540450167</v>
+        <v>1585.8880475510227</v>
       </c>
       <c r="L18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*L8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1706.1683797946373</v>
+        <v>1697.5798733006436</v>
       </c>
       <c r="M18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!$B$34*M8+'PyG 3 Años'!$B$35/12),"")</f>
-        <v>1869.422175503997</v>
+        <v>1835.047528864171</v>
       </c>
       <c r="N18" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(B18:M18)),"")</f>
-        <v>18325.916308364034</v>
+        <v>18271.77335301337</v>
       </c>
     </row>
     <row r="19">
@@ -7102,11 +7106,11 @@
       </c>
       <c r="H19" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",MAX(0,-E20)),"")</f>
-        <v>33267.80743402463</v>
+        <v>33156.24174266731</v>
       </c>
       <c r="K19" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",MAX(0,-H20)),"")</f>
-        <v>31336.718447834977</v>
+        <v>31266.146268621233</v>
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
@@ -7122,15 +7126,15 @@
       </c>
       <c r="E20" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(B17:D17)-SUM(B18:D18)-E19),"")</f>
-        <v>-33267.80743402463</v>
+        <v>-33156.24174266731</v>
       </c>
       <c r="H20" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(E17:G17)-SUM(E18:G18)-H19),"")</f>
-        <v>-31336.718447834977</v>
+        <v>-31266.146268621233</v>
       </c>
       <c r="K20" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(H17:J17)-SUM(H18:J18)-K19),"")</f>
-        <v>-29951.875682297996</v>
+        <v>-29956.404250137966</v>
       </c>
     </row>
     <row r="21">
@@ -7169,55 +7173,55 @@
       </c>
       <c r="B22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(B10:B16)+IF(B21="",0,B21)),"")</f>
-        <v>4086.0429857652007</v>
+        <v>6463.900764809811</v>
       </c>
       <c r="C22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(C10:C16)+IF(C21="",0,C21)),"")</f>
-        <v>-1906.6521062244046</v>
+        <v>-2718.451814803955</v>
       </c>
       <c r="D22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(D10:D16)+IF(D21="",0,D21)),"")</f>
-        <v>-4672.584208983507</v>
+        <v>-4823.53862396286</v>
       </c>
       <c r="E22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(E10:E16)+IF(E21="",0,E21)),"")</f>
-        <v>4620.218680990404</v>
+        <v>4451.788200620477</v>
       </c>
       <c r="F22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(F10:F16)+IF(F21="",0,F21)),"")</f>
-        <v>6854.140253997145</v>
+        <v>6667.869813871784</v>
       </c>
       <c r="G22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(G10:G16)+IF(G21="",0,G21)),"")</f>
-        <v>5894.282833116114</v>
+        <v>5689.911796746702</v>
       </c>
       <c r="H22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(H10:H16)+IF(H21="",0,H21)),"")</f>
-        <v>-4139.432772221761</v>
+        <v>-4337.184986548648</v>
       </c>
       <c r="I22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(I10:I16)+IF(I21="",0,I21)),"")</f>
-        <v>-1946.67614865986</v>
+        <v>-2684.607407655648</v>
       </c>
       <c r="J22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(J10:J16)+IF(J21="",0,J21)),"")</f>
-        <v>5844.928606807989</v>
+        <v>5792.3252344298635</v>
       </c>
       <c r="K22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(K10:K16)+IF(K21="",0,K21)),"")</f>
-        <v>5183.127836643649</v>
+        <v>4985.699859438402</v>
       </c>
       <c r="L22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(L10:L16)+IF(L21="",0,L21)),"")</f>
-        <v>8405.20376742574</v>
+        <v>8207.688666065671</v>
       </c>
       <c r="M22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(M10:M16)+IF(M21="",0,M21)),"")</f>
-        <v>6410.286482345559</v>
+        <v>5401.8543397388485</v>
       </c>
       <c r="N22" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",SUM(B22:M22)),"")</f>
-        <v>34632.88621100227</v>
+        <v>33097.25584275045</v>
       </c>
       <c r="O22" s="23" t="n"/>
     </row>
@@ -7229,51 +7233,51 @@
       </c>
       <c r="B23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'Inversión Inicial'!$B$18+B22),"")</f>
-        <v>66201.30480602956</v>
+        <v>68579.16258507417</v>
       </c>
       <c r="C23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",B23+C22),"")</f>
-        <v>64294.65269980515</v>
+        <v>65860.71077027022</v>
       </c>
       <c r="D23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",C23+D22),"")</f>
-        <v>59622.06849082164</v>
+        <v>61037.17214630736</v>
       </c>
       <c r="E23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",D23+E22),"")</f>
-        <v>64242.287171812044</v>
+        <v>65488.96034692784</v>
       </c>
       <c r="F23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",E23+F22),"")</f>
-        <v>71096.42742580919</v>
+        <v>72156.83016079963</v>
       </c>
       <c r="G23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",F23+G22),"")</f>
-        <v>76990.7102589253</v>
+        <v>77846.74195754633</v>
       </c>
       <c r="H23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",G23+H22),"")</f>
-        <v>72851.27748670355</v>
+        <v>73509.55697099768</v>
       </c>
       <c r="I23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",H23+I22),"")</f>
-        <v>70904.60133804369</v>
+        <v>70824.94956334203</v>
       </c>
       <c r="J23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",I23+J22),"")</f>
-        <v>76749.52994485167</v>
+        <v>76617.2747977719</v>
       </c>
       <c r="K23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",J23+K22),"")</f>
-        <v>81932.65778149532</v>
+        <v>81602.9746572103</v>
       </c>
       <c r="L23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",K23+L22),"")</f>
-        <v>90337.86154892106</v>
+        <v>89810.66332327598</v>
       </c>
       <c r="M23" s="24">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",L23+M22),"")</f>
-        <v>96748.14803126662</v>
+        <v>95212.51766301482</v>
       </c>
       <c r="N23" s="23" t="n"/>
       <c r="O23" s="23" t="n"/>
@@ -7286,7 +7290,7 @@
       </c>
       <c r="B24" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",IF(COUNT(B23:M23)=0,"",MIN(B23:M23))),"")</f>
-        <v>59622.06849082164</v>
+        <v>61037.17214630736</v>
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
@@ -7340,7 +7344,7 @@
       </c>
       <c r="B28" s="15">
         <f>IFERROR(IF('PyG 3 Años'!$B$11="","",'PyG 3 Años'!B43+'PyG 3 Años'!B31+'Financiación'!$B$116),"")</f>
-        <v>25207.729917629018</v>
+        <v>24229.77278660763</v>
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
@@ -9975,11 +9979,11 @@
       </c>
       <c r="E116" s="15">
         <f>IFERROR('PyG 3 Años'!B36-'PyG 3 Años'!B41+'PyG 3 Años'!B31+B116,"")</f>
-        <v>25207.729917629018</v>
+        <v>24229.77278660763</v>
       </c>
       <c r="F116" s="39">
         <f>IFERROR(IF(OR(D116="",D116=0),"",E116/D116),"")</f>
-        <v>3.370272165982183</v>
+        <v>3.2395193489306116</v>
       </c>
       <c r="H116" s="5" t="inlineStr">
         <is>
@@ -10145,7 +10149,7 @@
       </c>
       <c r="B123" s="40">
         <f>IFERROR(IF(COUNT(F116:F122)=0,"",MIN(F116:F122)),"")</f>
-        <v>3.370272165982183</v>
+        <v>3.2395193489306116</v>
       </c>
       <c r="C123" s="23" t="n"/>
       <c r="D123" s="23" t="n"/>
